--- a/IBM.xlsx
+++ b/IBM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{418FEC0F-1956-4C43-8BEB-AB390B1FC6DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5EE02FB-4335-438B-8DA0-07A51BB7D28F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{13969822-0D99-4296-BD6D-53BA0933144D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{13969822-0D99-4296-BD6D-53BA0933144D}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -201,7 +201,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -292,7 +292,7 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
@@ -651,7 +651,7 @@
         <v>3</v>
       </c>
       <c r="H2" s="8">
-        <v>258.2</v>
+        <v>210.52</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -674,7 +674,7 @@
       </c>
       <c r="H4" s="10">
         <f>+H3*H2</f>
-        <v>240518.26828439999</v>
+        <v>196103.43082584001</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -710,7 +710,7 @@
       </c>
       <c r="H7" s="10">
         <f>+H4-H5+H6</f>
-        <v>289235.26828439999</v>
+        <v>244820.43082584001</v>
       </c>
     </row>
   </sheetData>
@@ -935,7 +935,7 @@
         <v>21</v>
       </c>
       <c r="C6" s="11">
-        <f t="shared" ref="C6:H6" si="0">SUM(C3:C5)</f>
+        <f t="shared" ref="C6:G6" si="0">SUM(C3:C5)</f>
         <v>0</v>
       </c>
       <c r="D6" s="11">
@@ -2470,7 +2470,7 @@
         <v>43</v>
       </c>
       <c r="C31" s="7" t="e">
-        <f t="shared" ref="C31:J33" si="19">+(C4-C8)/C4</f>
+        <f t="shared" ref="C31:H33" si="19">+(C4-C8)/C4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D31" s="7" t="e">
